--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38674,7 +38674,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39406,7 +39406,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39467,7 +39467,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
@@ -623,7 +623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2330,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2712,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3090,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3155,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3220,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3285,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3537,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3602,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3732,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3858,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3988,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4423,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4488,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4553,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4618,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4809,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4874,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4939,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5313,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5378,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5626,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5817,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5947,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6134,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6321,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6386,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6642,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6772,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6898,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7150,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7215,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7341,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7406,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7532,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7784,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7975,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8101,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8166,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8231,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8605,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8853,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8918,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8983,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9109,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9174,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9239,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9304,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9369,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9495,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9682,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9869,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9934,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10182,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10434,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10690,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10877,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11003,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11190,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11572,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11637,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11702,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12072,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12450,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12637,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12767,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13023,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13271,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13401,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13466,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13531,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13978,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14043,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14295,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14852,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15421,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15551,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15738,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16108,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16238,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16303,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16433,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16498,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16685,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16750,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16815,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16941,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17071,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17136,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17717,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17973,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18103,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18168,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18294,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18359,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18424,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18550,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18798,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18989,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19054,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19119,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19367,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19432,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19562,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19749,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19814,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20005,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20444,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20509,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20574,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20700,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20765,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21261,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21326,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21574,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21700,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21830,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21960,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22086,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22151,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22277,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22915,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23045,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23297,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23488,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23553,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23744,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23931,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23996,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24061,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24191,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24443,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24634,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25268,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25394,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25459,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25524,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25589,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25719,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25910,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25975,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26162,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26227,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26422,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26617,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26682,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26747,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26812,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26877,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +26942,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27129,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27564,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27938,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28068,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28381,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28572,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28637,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28702,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28828,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28893,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28958,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29023,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29153,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29283,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29409,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29852,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30104,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30230,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30417,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30482,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30608,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30673,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30799,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +30925,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +30990,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31055,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31120,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31185,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31250,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31315,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31380,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31815,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31941,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32132,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32319,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32384,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32705,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32831,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32896,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32961,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33026,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33091,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33156,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33343,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33721,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33786,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33851,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +33916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +33981,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34359,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34424,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34741,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +34806,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34871,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +34936,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35635,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35700,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35891,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +35956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36647,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36773,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +36899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37025,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37090,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37155,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37281,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37529,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37594,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +37724,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +37915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +37980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38106,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +38236,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38301,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38622,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38687,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38817,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +38882,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +38947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39012,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39077,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39333,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39398,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39463,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39528,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39654,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +39841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +39906,11 @@
           <t>76.905.483-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +39971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40036,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40101,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40166,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40231,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40296,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +40422,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +40670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +40857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +40922,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +40987,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41243,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41308,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +41682,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +41869,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +41934,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +41999,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +42064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42129,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/may-2025.xlsx
@@ -2903,7 +2903,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4175,7 +4179,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5443,7 +5451,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5504,7 +5516,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7296,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7471,7 +7491,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7658,7 +7682,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9560,7 +9588,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9999,7 +10031,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10121,7 +10157,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11828,7 +11868,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11889,7 +11933,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13596,7 +13644,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14665,7 +14717,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15234,7 +15290,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15616,7 +15676,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19306,7 +19370,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19688,7 +19756,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20830,7 +20902,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21513,7 +21589,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23618,7 +23698,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27377,7 +27461,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27816,7 +27904,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29348,7 +29440,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29600,7 +29696,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29982,7 +30082,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30547,7 +30651,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30738,7 +30846,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30864,7 +30976,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33221,7 +33337,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34298,7 +34418,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34489,7 +34613,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36586,7 +36714,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36838,7 +36970,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36964,7 +37100,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37220,7 +37360,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38045,7 +38189,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38496,7 +38644,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39272,7 +39424,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40609,7 +40765,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40796,7 +40956,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41373,7 +41537,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41808,7 +41976,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
